--- a/tdp_system/templates/inventory_nxt_template.xlsx
+++ b/tdp_system/templates/inventory_nxt_template.xlsx
@@ -1888,11 +1888,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="358.8" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH PHÁT TRIỂN THƯƠNG MẠI THÀNH ĐẠT PHÁT</t>
-        </is>
-      </c>
+      <c r="A1" s="15" t="n"/>
       <c r="B1" s="16" t="n"/>
       <c r="C1" s="16" t="n"/>
       <c r="D1" s="9" t="n"/>
@@ -1907,11 +1903,7 @@
       <c r="S1" s="20" t="n"/>
     </row>
     <row r="2" ht="409.5" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
-        <is>
-          <t>Địa chỉ: Số 3/53/33/112A Ngô Quyền, Phường Máy Chai, Quận Ngô Quyền, Thành phố Hải Phòng</t>
-        </is>
-      </c>
+      <c r="A2" s="21" t="n"/>
       <c r="B2" s="16" t="n"/>
       <c r="C2" s="16" t="n"/>
       <c r="D2" s="9" t="n"/>
@@ -1925,11 +1917,7 @@
       <c r="R2" s="92" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="23" t="inlineStr">
-        <is>
-          <t>MST: 0201650135</t>
-        </is>
-      </c>
+      <c r="A3" s="23" t="n"/>
       <c r="B3" s="16" t="n"/>
       <c r="C3" s="16" t="n"/>
       <c r="D3" s="9" t="n"/>
